--- a/outputs/greener_grass_content_templates/greener_grass_content_templates.xlsx
+++ b/outputs/greener_grass_content_templates/greener_grass_content_templates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lydukhanhhan/Documents/MA_ResearchLog/outputs/greener_grass_content_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD96198-7EE6-8C45-A61E-343A07C78AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1CB162-7481-8249-9ED6-6CA1ABCB7975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30240" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
